--- a/DDA.xlsx
+++ b/DDA.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18082" uniqueCount="381">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21866" uniqueCount="381">
   <si>
     <t>Déclaration d'applicabilité</t>
   </si>

--- a/DDA.xlsx
+++ b/DDA.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21866" uniqueCount="381">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23370" uniqueCount="381">
   <si>
     <t>Déclaration d'applicabilité</t>
   </si>
